--- a/insurance_forms/027_life_insurance_policy_feedback_questionnaire--insurance_forms.xlsx
+++ b/insurance_forms/027_life_insurance_policy_feedback_questionnaire--insurance_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,7 +441,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
     <col width="40" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>policy_purchase_date</t>
+          <t>policy_purchase_date_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>When was the policy purchased?</t>
+          <t>Policy Purchase Date Range</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>policy_issuer</t>
+          <t>policy_issuer_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Who issued the policy?</t>
+          <t>Policy Issuer 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -750,7 +750,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>policy_benefit</t>
+          <t>policy_benefit_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>policy_deductible</t>
+          <t>policy_deductible_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>policy_premium</t>
+          <t>policy_premium_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>How much is the policy's premium?</t>
+          <t>Policy Premium 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>policy_purchaser_rating</t>
+          <t>policy_purchaser_rating_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>How would you rate the policy?</t>
+          <t>Policy Purchaser Rating 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>policy_purchaser_comment</t>
+          <t>policy_purchaser_comment_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Why did you choose this policy?</t>
+          <t>Policy Purchaser Comment 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>policy_issuer_rating</t>
+          <t>policy_issuer_rating_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>How would you rate the issuer?</t>
+          <t>Policy Issuer Rating 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Why did you choose this policy?</t>
+          <t>Policy Issuer Comment</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>policy_issuer_comment</t>
+          <t>policy_issuer_comment_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Why did you choose this policy?</t>
+          <t>Policy Issuer Comment 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>policy_purchaser_satisfaction</t>
+          <t>policy_purchaser_satisfaction_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>How satisfied are you with the policy?</t>
+          <t>Policy Purchaser Satisfaction 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="33" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1194,7 +1194,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>policy_purchase_date_choices</t>
+          <t>policy_purchase_date_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1211,7 +1211,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>policy_purchase_date_choices</t>
+          <t>policy_purchase_date_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1228,7 +1228,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>policy_issuer_choices</t>
+          <t>policy_issuer_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1245,7 +1245,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>policy_issuer_choices</t>
+          <t>policy_issuer_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1262,7 +1262,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>policy_benefit_choices</t>
+          <t>policy_benefit_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1279,7 +1279,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>policy_benefit_choices</t>
+          <t>policy_benefit_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1296,7 +1296,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>policy_deductible_choices</t>
+          <t>policy_deductible_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1313,7 +1313,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>policy_deductible_choices</t>
+          <t>policy_deductible_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1330,7 +1330,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>policy_deductible_choices</t>
+          <t>policy_deductible_2_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1347,7 +1347,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>policy_deductible_choices</t>
+          <t>policy_deductible_2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1364,117 +1364,83 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>policy_purchaser_rating_choices</t>
+          <t>policy_purchaser_rating_2_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>policy_purchaser_rating_choices</t>
+          <t>policy_purchaser_rating_2_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>policy_purchaser_rating_choices</t>
+          <t>policy_purchaser_rating_2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>dissatisfied</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>policy_purchaser_rating_choices</t>
+          <t>policy_issuer_rating_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>policy_purchaser_rating_choices</t>
+          <t>policy_issuer_rating_2_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>policy_issuer_rating_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>policy_issuer_rating_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>fair</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
         <is>
           <t>Fair</t>
         </is>
